--- a/정기/BM/컨텐츠 기획 모음/컨텐츠 기획 능력치.xlsx
+++ b/정기/BM/컨텐츠 기획 모음/컨텐츠 기획 능력치.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjg19\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\BM\컨텐츠 기획 모음\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{782B6803-EFEB-4D54-9BE7-464968EC2F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B34829-1E5F-4296-BA55-7199326B848A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4455" yWindow="4020" windowWidth="21810" windowHeight="11295" activeTab="1" xr2:uid="{3BF25590-3113-4B5B-812C-AC5FDFD7BF9A}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21810" windowHeight="11295" activeTab="2" xr2:uid="{3BF25590-3113-4B5B-812C-AC5FDFD7BF9A}"/>
   </bookViews>
   <sheets>
     <sheet name="패기" sheetId="1" r:id="rId1"/>
     <sheet name="신수" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="119">
   <si>
     <t>패기</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -169,6 +170,3053 @@
   <si>
     <t>성급</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>타입</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>속성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>확률1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>확률2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>총확률</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>특정</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>성급 됨</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>물</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>불</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>풀</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>등급</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상승</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>필요</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재료</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>상세</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>3★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성장</t>
+    </r>
+  </si>
+  <si>
+    <t>4성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>4★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>(4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>단계 모든속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*1</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 4)</t>
+    </r>
+  </si>
+  <si>
+    <t>7성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3) + (6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>8성</t>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2) + (6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>9성</t>
+  </si>
+  <si>
+    <r>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2) + (6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>10성</t>
+  </si>
+  <si>
+    <r>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 11</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + (9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✨</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외형</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변신</t>
+    </r>
+  </si>
+  <si>
+    <t>11성</t>
+  </si>
+  <si>
+    <r>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 12</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>12성</t>
+  </si>
+  <si>
+    <r>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>동일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>13성</t>
+  </si>
+  <si>
+    <r>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 14</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + (10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>14성</t>
+  </si>
+  <si>
+    <r>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 15</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2) + (5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2) + (11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>15성</t>
+  </si>
+  <si>
+    <r>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 16</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(9</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + (12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✨</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>차</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>외형</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>변신</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최종</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>16성</t>
+  </si>
+  <si>
+    <r>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>17성</t>
+  </si>
+  <si>
+    <r>
+      <t>17</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 18</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>18성</t>
+  </si>
+  <si>
+    <r>
+      <t>18</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1) + (15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+  </si>
+  <si>
+    <t>19성</t>
+  </si>
+  <si>
+    <r>
+      <t>19</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> → 20</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>★</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>(12</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>본체</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> + (15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>속성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>👑</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> MAX </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="굴림"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>레벨</t>
+    </r>
+  </si>
+  <si>
+    <t>20성</t>
+  </si>
+  <si>
+    <t>1회</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.7성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+  </si>
+  <si>
+    <t>환산 가치</t>
+  </si>
+  <si>
+    <t>기대비용</t>
+  </si>
+  <si>
+    <t>3성</t>
+  </si>
+  <si>
+    <t>162원</t>
+  </si>
+  <si>
+    <t>4성</t>
+  </si>
+  <si>
+    <t>648원</t>
+  </si>
+  <si>
+    <t>5성</t>
+  </si>
+  <si>
+    <t>2,594원</t>
   </si>
 </sst>
 </file>
@@ -178,7 +3226,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +3267,63 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="굴림"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -251,12 +3356,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -274,7 +3394,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -321,6 +3441,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1828,4 +4975,1046 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5333A017-BF22-449C-A4AA-07831A706804}">
+  <dimension ref="A1:S35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="7" max="7" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.625" customWidth="1"/>
+    <col min="12" max="12" width="55.25" customWidth="1"/>
+    <col min="13" max="13" width="19.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G2">
+        <v>600</v>
+      </c>
+      <c r="O2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>46</v>
+      </c>
+      <c r="R2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="16">
+        <v>0.34</v>
+      </c>
+      <c r="F3" s="17">
+        <f>E3*D3</f>
+        <v>0.17</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" ref="G3:G19" si="0">G$2/F3</f>
+        <v>3529.411764705882</v>
+      </c>
+      <c r="H3" s="1">
+        <v>3529.411764705882</v>
+      </c>
+      <c r="I3">
+        <f>G2/D3</f>
+        <v>1200</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="E4" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="F4" s="17">
+        <f t="shared" ref="F4:F20" si="1">E4*D4</f>
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="0"/>
+        <v>3636.363636363636</v>
+      </c>
+      <c r="H4" s="1">
+        <v>3636.363636363636</v>
+      </c>
+      <c r="I4">
+        <v>1200</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" s="1">
+        <f>162*3*3</f>
+        <v>1458</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" ref="Q4:R4" si="2">162*3*3</f>
+        <v>1458</v>
+      </c>
+      <c r="R4" s="1">
+        <f t="shared" si="2"/>
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="F5" s="17">
+        <f t="shared" si="1"/>
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="0"/>
+        <v>3636.363636363636</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3636.363636363636</v>
+      </c>
+      <c r="I5">
+        <v>1200</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="21"/>
+      <c r="O5" t="s">
+        <v>58</v>
+      </c>
+      <c r="P5">
+        <f>648*3*3+P4*3</f>
+        <v>10206</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:R5" si="3">648*3*3+Q4*3</f>
+        <v>10206</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>10206</v>
+      </c>
+      <c r="S5">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="E6" s="16">
+        <v>0.34</v>
+      </c>
+      <c r="F6" s="17">
+        <f t="shared" si="1"/>
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>4411.7647058823522</v>
+      </c>
+      <c r="H6" s="1">
+        <v>4411.7647058823522</v>
+      </c>
+      <c r="I6">
+        <f>G2/D6</f>
+        <v>1500</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6">
+        <f>P5*3+P5*3+P5*3</f>
+        <v>91854</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" ref="Q6:R6" si="4">Q5*3+Q5*3+Q5*3</f>
+        <v>91854</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="4"/>
+        <v>91854</v>
+      </c>
+      <c r="S6">
+        <f>60000+R6</f>
+        <v>151854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="E7" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="F7" s="17">
+        <f t="shared" si="1"/>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>4545.454545454545</v>
+      </c>
+      <c r="H7" s="1">
+        <v>4545.454545454545</v>
+      </c>
+      <c r="I7">
+        <v>1500</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="M7" s="20"/>
+      <c r="N7" s="21"/>
+      <c r="O7" t="s">
+        <v>65</v>
+      </c>
+      <c r="P7">
+        <f>P5*4+P6*3</f>
+        <v>316386</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" ref="Q7:R7" si="5">Q5*4+Q6*3</f>
+        <v>316386</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="5"/>
+        <v>316386</v>
+      </c>
+      <c r="S7">
+        <f>S5*4</f>
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="E8" s="16">
+        <v>0.33</v>
+      </c>
+      <c r="F8" s="17">
+        <f t="shared" si="1"/>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>4545.454545454545</v>
+      </c>
+      <c r="H8" s="1">
+        <v>4545.454545454545</v>
+      </c>
+      <c r="I8">
+        <v>1500</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="20"/>
+      <c r="N8" s="21"/>
+      <c r="O8" t="s">
+        <v>68</v>
+      </c>
+      <c r="P8">
+        <f>P5*3+P6</f>
+        <v>122472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H9">
+        <v>20000</v>
+      </c>
+      <c r="I9">
+        <f>G2/D9</f>
+        <v>6000</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M9" s="20"/>
+      <c r="N9" s="21"/>
+      <c r="O9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F10" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H10">
+        <v>20000</v>
+      </c>
+      <c r="I10">
+        <v>6000</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" s="20"/>
+      <c r="N10" s="21"/>
+      <c r="O10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="48" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F11" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H11">
+        <v>20000</v>
+      </c>
+      <c r="I11">
+        <v>6000</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="19"/>
+      <c r="N11" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="O11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F12" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H12">
+        <v>20000</v>
+      </c>
+      <c r="I12">
+        <v>6000</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="M12" s="20"/>
+      <c r="N12" s="21"/>
+      <c r="O12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H13">
+        <v>20000</v>
+      </c>
+      <c r="I13">
+        <v>6000</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="M13" s="20"/>
+      <c r="N13" s="21"/>
+      <c r="O13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F14" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H14">
+        <v>20000</v>
+      </c>
+      <c r="I14">
+        <v>6000</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="N14" s="21"/>
+      <c r="O14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F15" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H15">
+        <v>20000</v>
+      </c>
+      <c r="I15">
+        <v>6000</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="20"/>
+      <c r="N15" s="21"/>
+      <c r="O15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="49.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G16" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H16">
+        <v>20000</v>
+      </c>
+      <c r="I16">
+        <v>6000</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M16" s="19"/>
+      <c r="N16" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="O16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="17">
+        <f t="shared" si="1"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="G17" s="1">
+        <f t="shared" si="0"/>
+        <v>59999.999999999985</v>
+      </c>
+      <c r="H17">
+        <v>20000</v>
+      </c>
+      <c r="I17">
+        <v>6000</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="L17" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="M17" s="20"/>
+      <c r="N17" s="21"/>
+      <c r="O17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="16">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="F18" s="17">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="G18" s="1">
+        <f t="shared" si="0"/>
+        <v>180000</v>
+      </c>
+      <c r="H18">
+        <f>G18/3</f>
+        <v>60000</v>
+      </c>
+      <c r="I18">
+        <v>6000</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="M18" s="20"/>
+      <c r="N18" s="21"/>
+      <c r="O18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E19" s="16">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="F19" s="17">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="G19" s="1">
+        <f t="shared" si="0"/>
+        <v>180000</v>
+      </c>
+      <c r="H19">
+        <f t="shared" ref="H19:H20" si="6">G19/3</f>
+        <v>60000</v>
+      </c>
+      <c r="I19">
+        <v>6000</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="L19" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="M19" s="20"/>
+      <c r="N19" s="21"/>
+      <c r="O19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="32.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="E20" s="16">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="F20" s="17">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="G20" s="1">
+        <f>G$2/F20</f>
+        <v>180000</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="6"/>
+        <v>60000</v>
+      </c>
+      <c r="I20">
+        <v>6000</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="M20" s="19"/>
+      <c r="N20" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="O20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="F21" s="23">
+        <f>SUM(F3:F20)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>50</v>
+      </c>
+      <c r="H25">
+        <f>G25/100</f>
+        <v>0.5</v>
+      </c>
+      <c r="I25">
+        <f>H25*F25</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>40</v>
+      </c>
+      <c r="H26">
+        <f t="shared" ref="H26:H27" si="7">G26/100</f>
+        <v>0.4</v>
+      </c>
+      <c r="I26">
+        <f t="shared" ref="I26:I27" si="8">H26*F26</f>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E27">
+        <v>5</v>
+      </c>
+      <c r="F27">
+        <v>16</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="7"/>
+        <v>0.1</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="8"/>
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H28">
+        <v>600</v>
+      </c>
+      <c r="I28">
+        <f>SUM(I25:I27)</f>
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H30">
+        <v>600</v>
+      </c>
+      <c r="I30" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="F32" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F33" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="15">
+        <v>1</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="I33">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F34" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G34" s="15">
+        <v>4</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="I34">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="35" spans="6:9" x14ac:dyDescent="0.3">
+      <c r="F35" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" s="15">
+        <v>16</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="I35">
+        <v>2594</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/정기/BM/컨텐츠 기획 모음/컨텐츠 기획 능력치.xlsx
+++ b/정기/BM/컨텐츠 기획 모음/컨텐츠 기획 능력치.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JJG\엑셀\정기\BM\컨텐츠 기획 모음\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B34829-1E5F-4296-BA55-7199326B848A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0583F443-51A1-4BA9-9789-B147CDEB5E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21810" windowHeight="11295" activeTab="2" xr2:uid="{3BF25590-3113-4B5B-812C-AC5FDFD7BF9A}"/>
+    <workbookView xWindow="690" yWindow="1125" windowWidth="21810" windowHeight="11295" activeTab="1" xr2:uid="{3BF25590-3113-4B5B-812C-AC5FDFD7BF9A}"/>
   </bookViews>
   <sheets>
     <sheet name="패기" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="283">
   <si>
     <t>패기</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -3217,16 +3217,644 @@
   </si>
   <si>
     <t>2,594원</t>
+  </si>
+  <si>
+    <t>신수 테스트 고돌</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누적다이아</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고성급(빛)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고성급(일반)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>200만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8성,8성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300만</t>
+  </si>
+  <si>
+    <t>11성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>400만</t>
+  </si>
+  <si>
+    <t>5성,5성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>500만</t>
+  </si>
+  <si>
+    <t>600만</t>
+  </si>
+  <si>
+    <t>7성,5성(4)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>700만</t>
+  </si>
+  <si>
+    <t>9성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7성,6성,5성(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성,8성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>800만</t>
+  </si>
+  <si>
+    <t>10성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성,5성(3)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성,7성(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>900만</t>
+  </si>
+  <si>
+    <t>9성,5성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>14성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000만</t>
+  </si>
+  <si>
+    <t>9성,5성(4)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성,5성(5)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성,10성,8성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성,6성,5성(4)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11성,9성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1800만</t>
+  </si>
+  <si>
+    <t>9성,6성,5성(5)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000만</t>
+  </si>
+  <si>
+    <t>14성,11성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7성,6성,5성(3)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>16성(멈춤)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2300만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>14성,12성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>16성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2600만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15성,12성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6성(3),5성(5)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2900만</t>
+  </si>
+  <si>
+    <t>15성,14성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(7)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3200만</t>
+  </si>
+  <si>
+    <t>9성,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>불불빛</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(3)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9성,7성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(5)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10성,9성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(8)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12성,11성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6성,5성(11)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13성,11성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(10)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1200만</t>
+  </si>
+  <si>
+    <t>5성(9개)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1400만</t>
+  </si>
+  <si>
+    <t>5성(5개)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1600만</t>
+  </si>
+  <si>
+    <t>5성(10개)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(13개)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(20개)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15성,13성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛빛불</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>150만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(1)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>300만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>450만</t>
+  </si>
+  <si>
+    <t>750만</t>
+  </si>
+  <si>
+    <t>5성(4)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11성,10성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1050만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1350만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1650만</t>
+  </si>
+  <si>
+    <t>5성(12)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1950만</t>
+  </si>
+  <si>
+    <t>6성(2),5성(11)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2250만</t>
+  </si>
+  <si>
+    <t>6성(2),5성(15)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2550만</t>
+  </si>
+  <si>
+    <t>11성,11성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6성(2).5성(5)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2850만</t>
+  </si>
+  <si>
+    <t>6성(2),5성(7)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3150만</t>
+  </si>
+  <si>
+    <t>12성,12성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6성(1),5성(8)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3450만</t>
+  </si>
+  <si>
+    <t>6성(1),5성(10)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3750만</t>
+  </si>
+  <si>
+    <t>13성,12성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5성(11)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12성(1),10성(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4050만</t>
+  </si>
+  <si>
+    <t>14성,13성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12성(1),9성(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4350만</t>
+  </si>
+  <si>
+    <t>7성(1),6성(1),5성(1)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4650만</t>
+  </si>
+  <si>
+    <t>14성,14성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>7성(2),5성(2)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4950만</t>
+  </si>
+  <si>
+    <t>15성,15성</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>빛불물</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>총 공격력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스테이지 클리어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(5)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>8,7,6(6)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>600만</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(10)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,7,6(6)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>5(18)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6(3)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,5(22)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6(6)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1500만</t>
+  </si>
+  <si>
+    <t>5(23)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15성(완성)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(원숭이) 15861.3%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>15성(원숭이) 몰빵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>6(2),5(8)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(호랑이) 1631.1%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100만</t>
+  </si>
+  <si>
+    <t>6(2),5(4)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400만</t>
+  </si>
+  <si>
+    <t>5(3)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2700만</t>
+  </si>
+  <si>
+    <t>6,5(3)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3000만</t>
+  </si>
+  <si>
+    <t>5(6)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,9,8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300만</t>
+  </si>
+  <si>
+    <t>5(8)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>12,11,8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600만</t>
+  </si>
+  <si>
+    <t>8,5(5)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>13,11</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3900만</t>
+  </si>
+  <si>
+    <t>5(7)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4200만</t>
+  </si>
+  <si>
+    <t>5(11)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>15성,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15성(완성)</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>4500만</t>
+  </si>
+  <si>
+    <t>4800만</t>
+  </si>
+  <si>
+    <t>5100만</t>
+  </si>
+  <si>
+    <t>5400만</t>
+  </si>
+  <si>
+    <t>5700만</t>
+  </si>
+  <si>
+    <t>(호랑이) 158163.8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(뱀) 15073.3%</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>신수 테스트 레레</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3324,8 +3952,17 @@
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3355,8 +3992,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3379,6 +4046,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3394,7 +4076,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3470,6 +4152,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="백분율" xfId="2" builtinId="5"/>
@@ -3488,6 +4212,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>11801</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E905F4F-3EF7-46BC-9F0C-6254F10A723E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5334000" y="11801"/>
+          <a:ext cx="3190875" cy="5436499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4078,7 +4851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A929A37-4F69-4716-BFD6-800ED9B3FEBC}">
-  <dimension ref="C3:T34"/>
+  <dimension ref="C3:T130"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="3" spans="3:20" x14ac:dyDescent="0.3">
@@ -4949,7 +5722,7 @@
         <v>31375</v>
       </c>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C33">
         <v>14</v>
       </c>
@@ -4960,7 +5733,7 @@
         <v>36585</v>
       </c>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C34">
         <v>15</v>
       </c>
@@ -4970,10 +5743,1571 @@
       <c r="E34" s="15">
         <v>45150</v>
       </c>
+    </row>
+    <row r="37" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D37" t="s">
+        <v>119</v>
+      </c>
+      <c r="N37" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="38" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D38" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H38" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+    </row>
+    <row r="39" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D39" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+    </row>
+    <row r="40" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D40" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H40" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+    </row>
+    <row r="41" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D41" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="H41" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="I41" s="25"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="25"/>
+    </row>
+    <row r="42" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D42" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H42" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="I42" s="25"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="25"/>
+    </row>
+    <row r="43" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D43" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F43" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="G43" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="H43" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="I43" s="25"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="25"/>
+    </row>
+    <row r="44" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D44" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="G44" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H44" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+    </row>
+    <row r="45" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D45" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G45" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H45" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="I45" s="25"/>
+      <c r="J45" s="25"/>
+      <c r="K45" s="25"/>
+    </row>
+    <row r="46" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D46" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="G46" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H46" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="I46" s="25"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="25"/>
+    </row>
+    <row r="47" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D47" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F47" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="G47" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="25"/>
+    </row>
+    <row r="48" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="D48" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F48" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H48" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="I48" s="25"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="25"/>
+    </row>
+    <row r="49" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D49" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="G49" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H49" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="I49" s="25"/>
+      <c r="J49" s="25"/>
+      <c r="K49" s="25"/>
+    </row>
+    <row r="50" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D50" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="E50" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G50" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="I50" s="25"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="25"/>
+    </row>
+    <row r="51" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D51" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="G51" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="25"/>
+    </row>
+    <row r="52" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D52" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G52" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H52" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="I52" s="25"/>
+      <c r="J52" s="25"/>
+      <c r="K52" s="25"/>
+    </row>
+    <row r="53" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D53" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="G53" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="H53" s="25"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="25"/>
+      <c r="K53" s="25"/>
+    </row>
+    <row r="54" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D54" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F54" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="G54" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="H54" s="25"/>
+      <c r="I54" s="25"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+    </row>
+    <row r="55" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D55" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="F55" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="G55" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+      <c r="J55" s="25"/>
+      <c r="K55" s="25"/>
+    </row>
+    <row r="56" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D56" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F56" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="G56" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="25"/>
+    </row>
+    <row r="57" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D57" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="E57" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F57" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+      <c r="J57" s="25"/>
+      <c r="K57" s="25"/>
+    </row>
+    <row r="58" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+    </row>
+    <row r="59" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
+      <c r="H59" s="25"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="25"/>
+    </row>
+    <row r="60" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D60" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="E60" s="25"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="25"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="25"/>
+      <c r="K60" s="25"/>
+    </row>
+    <row r="61" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="25"/>
+      <c r="K61" s="25"/>
+    </row>
+    <row r="62" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D62" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F62" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G62" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H62" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I62" s="25"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="25"/>
+    </row>
+    <row r="63" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D63" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="G63" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="H63" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="I63" s="25"/>
+      <c r="J63" s="25"/>
+      <c r="K63" s="25"/>
+    </row>
+    <row r="64" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D64" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="G64" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="H64" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="I64" s="25"/>
+      <c r="J64" s="25"/>
+      <c r="K64" s="25"/>
+    </row>
+    <row r="65" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D65" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F65" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G65" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="H65" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I65" s="25"/>
+      <c r="J65" s="25"/>
+      <c r="K65" s="25"/>
+    </row>
+    <row r="66" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D66" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F66" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="G66" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="H66" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="I66" s="25"/>
+      <c r="J66" s="25"/>
+      <c r="K66" s="25"/>
+    </row>
+    <row r="67" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D67" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F67" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="G67" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25"/>
+      <c r="J67" s="25"/>
+      <c r="K67" s="25"/>
+    </row>
+    <row r="68" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D68" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="F68" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="G68" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="25"/>
+      <c r="K68" s="25"/>
+    </row>
+    <row r="69" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D69" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F69" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G69" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="25"/>
+    </row>
+    <row r="70" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D70" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F70" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="G70" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="H70" s="25"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="25"/>
+      <c r="K70" s="25"/>
+    </row>
+    <row r="71" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D71" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F71" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="G71" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="H71" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I71" s="25"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="25"/>
+    </row>
+    <row r="72" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D72" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="E72" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="F72" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="G72" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="H72" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="I72" s="25"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="25"/>
+    </row>
+    <row r="73" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D73" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="25"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="25"/>
+    </row>
+    <row r="74" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D74" s="25"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="25"/>
+      <c r="J74" s="25"/>
+      <c r="K74" s="25"/>
+    </row>
+    <row r="75" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D75" s="25"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="25"/>
+    </row>
+    <row r="76" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D76" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+    </row>
+    <row r="77" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
+      <c r="H77" s="25"/>
+      <c r="I77" s="25"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="25"/>
+    </row>
+    <row r="78" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D78" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E78" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F78" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G78" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H78" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I78" s="25"/>
+      <c r="J78" s="25"/>
+      <c r="K78" s="25"/>
+    </row>
+    <row r="79" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D79" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="E79" s="29"/>
+      <c r="F79" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="G79" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="H79" s="25"/>
+      <c r="I79" s="25"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="25"/>
+    </row>
+    <row r="80" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D80" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="E80" s="29"/>
+      <c r="F80" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="G80" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="H80" s="25"/>
+      <c r="I80" s="25"/>
+      <c r="J80" s="25"/>
+      <c r="K80" s="25"/>
+    </row>
+    <row r="81" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D81" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="E81" s="29"/>
+      <c r="F81" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="G81" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="H81" s="25"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="25"/>
+    </row>
+    <row r="82" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D82" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E82" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F82" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="G82" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="H82" s="25"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="25"/>
+    </row>
+    <row r="83" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D83" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="E83" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F83" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="G83" s="29" t="s">
+        <v>203</v>
+      </c>
+      <c r="H83" s="25"/>
+      <c r="I83" s="25"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="25"/>
+    </row>
+    <row r="84" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D84" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E84" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F84" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="G84" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H84" s="25"/>
+      <c r="I84" s="25"/>
+      <c r="J84" s="25"/>
+      <c r="K84" s="25"/>
+    </row>
+    <row r="85" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D85" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="E85" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F85" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H85" s="25"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
+    </row>
+    <row r="86" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D86" s="28" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="G86" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="H86" s="25"/>
+      <c r="I86" s="25"/>
+      <c r="J86" s="25"/>
+      <c r="K86" s="25"/>
+    </row>
+    <row r="87" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D87" s="28" t="s">
+        <v>208</v>
+      </c>
+      <c r="E87" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="F87" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="G87" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="H87" s="25"/>
+      <c r="I87" s="25"/>
+      <c r="J87" s="25"/>
+      <c r="K87" s="25"/>
+    </row>
+    <row r="88" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D88" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="F88" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="G88" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H88" s="25"/>
+      <c r="I88" s="25"/>
+      <c r="J88" s="25"/>
+      <c r="K88" s="25"/>
+    </row>
+    <row r="89" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D89" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="E89" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="F89" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="G89" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H89" s="25"/>
+      <c r="I89" s="25"/>
+      <c r="J89" s="25"/>
+      <c r="K89" s="25"/>
+    </row>
+    <row r="90" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D90" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="E90" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="F90" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="G90" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H90" s="25"/>
+      <c r="I90" s="25"/>
+      <c r="J90" s="25"/>
+      <c r="K90" s="30"/>
+    </row>
+    <row r="91" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D91" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="E91" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="F91" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="G91" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="H91" s="25"/>
+      <c r="I91" s="25"/>
+      <c r="J91" s="25"/>
+      <c r="K91" s="25"/>
+    </row>
+    <row r="92" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D92" s="28" t="s">
+        <v>220</v>
+      </c>
+      <c r="E92" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="F92" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="G92" s="29" t="s">
+        <v>169</v>
+      </c>
+      <c r="H92" s="25"/>
+      <c r="I92" s="25"/>
+      <c r="J92" s="25"/>
+      <c r="K92" s="25"/>
+    </row>
+    <row r="93" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D93" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="E93" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="F93" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="G93" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H93" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="I93" s="25"/>
+      <c r="J93" s="25"/>
+      <c r="K93" s="25"/>
+    </row>
+    <row r="94" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D94" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="E94" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="G94" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H94" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="I94" s="25"/>
+      <c r="J94" s="25"/>
+      <c r="K94" s="25"/>
+    </row>
+    <row r="95" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D95" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="E95" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="G95" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H95" s="25"/>
+      <c r="I95" s="25"/>
+      <c r="J95" s="25"/>
+      <c r="K95" s="25"/>
+    </row>
+    <row r="96" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D96" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="E96" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="G96" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H96" s="25"/>
+      <c r="I96" s="25"/>
+      <c r="J96" s="25"/>
+      <c r="K96" s="25"/>
+    </row>
+    <row r="97" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D97" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="E97" s="29" t="s">
+        <v>235</v>
+      </c>
+      <c r="F97" s="25"/>
+      <c r="G97" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H97" s="25"/>
+      <c r="I97" s="25"/>
+      <c r="J97" s="25"/>
+      <c r="K97" s="25"/>
+    </row>
+    <row r="98" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D98" s="25"/>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="29"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="25"/>
+      <c r="J98" s="25"/>
+      <c r="K98" s="25"/>
+    </row>
+    <row r="99" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D99" s="25"/>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="25"/>
+      <c r="H99" s="25"/>
+      <c r="I99" s="25"/>
+      <c r="J99" s="25"/>
+      <c r="K99" s="25"/>
+    </row>
+    <row r="100" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D100" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="E100" s="25"/>
+      <c r="F100" s="25"/>
+      <c r="G100" s="25"/>
+      <c r="H100" s="25"/>
+      <c r="I100" s="25"/>
+      <c r="J100" s="25"/>
+      <c r="K100" s="25"/>
+    </row>
+    <row r="101" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D101" s="25"/>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
+      <c r="H101" s="25"/>
+      <c r="I101" s="25"/>
+      <c r="J101" s="25"/>
+      <c r="K101" s="25"/>
+    </row>
+    <row r="102" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D102" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E102" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="F102" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G102" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H102" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I102" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="J102" s="32" t="s">
+        <v>238</v>
+      </c>
+      <c r="K102" s="25"/>
+    </row>
+    <row r="103" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D103" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="E103" s="34"/>
+      <c r="F103" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="G103" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="H103" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="I103" s="36">
+        <v>2.82</v>
+      </c>
+      <c r="J103" s="32"/>
+      <c r="K103" s="25"/>
+    </row>
+    <row r="104" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D104" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="E104" s="34"/>
+      <c r="F104" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="G104" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="H104" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="I104" s="36">
+        <v>7.8380000000000001</v>
+      </c>
+      <c r="J104" s="32"/>
+      <c r="K104" s="25"/>
+    </row>
+    <row r="105" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D105" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="E105" s="34"/>
+      <c r="F105" s="25" t="s">
+        <v>244</v>
+      </c>
+      <c r="G105" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="H105" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="I105" s="36">
+        <v>34.564</v>
+      </c>
+      <c r="J105" s="32"/>
+      <c r="K105" s="25"/>
+    </row>
+    <row r="106" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D106" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="E106" s="34"/>
+      <c r="F106" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="G106" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="H106" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="I106" s="36">
+        <v>73.888999999999996</v>
+      </c>
+      <c r="J106" s="32"/>
+      <c r="K106" s="25"/>
+    </row>
+    <row r="107" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D107" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="E107" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F107" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="G107" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="H107" s="25"/>
+      <c r="I107" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="J107" s="32"/>
+      <c r="K107" s="25" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="108" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D108" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="E108" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F108" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="G108" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="H108" s="25"/>
+      <c r="I108" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="J108" s="32"/>
+      <c r="K108" s="25"/>
+    </row>
+    <row r="109" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D109" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="E109" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="G109" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="H109" s="25"/>
+      <c r="I109" s="36">
+        <v>50.5</v>
+      </c>
+      <c r="J109" s="32"/>
+      <c r="K109" s="25"/>
+    </row>
+    <row r="110" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D110" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="E110" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="F110" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="G110" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="H110" s="25"/>
+      <c r="I110" s="36">
+        <v>158.613</v>
+      </c>
+      <c r="J110" s="32"/>
+      <c r="K110" s="25"/>
+    </row>
+    <row r="111" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D111" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="E111" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="F111" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="G111" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="H111" s="25"/>
+      <c r="I111" s="36">
+        <v>158.613</v>
+      </c>
+      <c r="J111" s="32"/>
+      <c r="K111" s="25"/>
+    </row>
+    <row r="112" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D112" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="E112" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="F112" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="G112" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="H112" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="I112" s="36">
+        <v>500.5</v>
+      </c>
+      <c r="J112" s="32"/>
+      <c r="K112" s="25"/>
+    </row>
+    <row r="113" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D113" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="E113" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="F113" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="G113" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="H113" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="I113" s="36">
+        <v>500.5</v>
+      </c>
+      <c r="J113" s="32"/>
+      <c r="K113" s="25"/>
+    </row>
+    <row r="114" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D114" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="E114" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="F114" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G114" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="H114" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="I114" s="36">
+        <v>500.5</v>
+      </c>
+      <c r="J114" s="32"/>
+      <c r="K114" s="25"/>
+    </row>
+    <row r="115" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D115" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="E115" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="F115" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="G115" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="H115" s="25"/>
+      <c r="I115" s="36">
+        <v>1581.6379999999999</v>
+      </c>
+      <c r="J115" s="32"/>
+      <c r="K115" s="25"/>
+    </row>
+    <row r="116" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D116" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="E116" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="F116" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="G116" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="H116" s="25"/>
+      <c r="I116" s="36">
+        <v>1581.6379999999999</v>
+      </c>
+      <c r="J116" s="32"/>
+      <c r="K116" s="25"/>
+    </row>
+    <row r="117" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D117" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="E117" s="34"/>
+      <c r="F117" s="25"/>
+      <c r="G117" s="35"/>
+      <c r="H117" s="25"/>
+      <c r="I117" s="36"/>
+      <c r="J117" s="32"/>
+      <c r="K117" s="25"/>
+    </row>
+    <row r="118" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D118" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="E118" s="34"/>
+      <c r="F118" s="25"/>
+      <c r="G118" s="35"/>
+      <c r="H118" s="25"/>
+      <c r="I118" s="31"/>
+      <c r="J118" s="32"/>
+      <c r="K118" s="25"/>
+    </row>
+    <row r="119" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D119" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="E119" s="34"/>
+      <c r="F119" s="25"/>
+      <c r="G119" s="35"/>
+      <c r="H119" s="25"/>
+      <c r="I119" s="31"/>
+      <c r="J119" s="32"/>
+      <c r="K119" s="25"/>
+    </row>
+    <row r="120" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D120" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="E120" s="34"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="35"/>
+      <c r="H120" s="25"/>
+      <c r="I120" s="31"/>
+      <c r="J120" s="32"/>
+      <c r="K120" s="25"/>
+    </row>
+    <row r="121" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D121" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="E121" s="34"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="35"/>
+      <c r="H121" s="25"/>
+      <c r="I121" s="31"/>
+      <c r="J121" s="32"/>
+      <c r="K121" s="25"/>
+    </row>
+    <row r="122" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D122" s="25"/>
+      <c r="E122" s="25"/>
+      <c r="F122" s="25"/>
+      <c r="G122" s="25"/>
+      <c r="H122" s="25"/>
+      <c r="I122" s="25"/>
+      <c r="J122" s="25"/>
+      <c r="K122" s="25"/>
+    </row>
+    <row r="123" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D123" s="25"/>
+      <c r="E123" s="25"/>
+      <c r="F123" s="25"/>
+      <c r="G123" s="25"/>
+      <c r="H123" s="25"/>
+      <c r="I123" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="J123" s="25"/>
+      <c r="K123" s="25"/>
+    </row>
+    <row r="124" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D124" s="25"/>
+      <c r="E124" s="25"/>
+      <c r="F124" s="25"/>
+      <c r="G124" s="25"/>
+      <c r="H124" s="25"/>
+      <c r="I124" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="J124" s="25"/>
+      <c r="K124" s="25"/>
+    </row>
+    <row r="125" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D125" s="25"/>
+      <c r="E125" s="25"/>
+      <c r="F125" s="25"/>
+      <c r="G125" s="25"/>
+      <c r="H125" s="25"/>
+      <c r="I125" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="J125" s="25"/>
+      <c r="K125" s="25"/>
+    </row>
+    <row r="126" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D126" s="25"/>
+      <c r="E126" s="25"/>
+      <c r="F126" s="25"/>
+      <c r="G126" s="25"/>
+      <c r="H126" s="25"/>
+      <c r="I126" s="25"/>
+      <c r="J126" s="25"/>
+      <c r="K126" s="25"/>
+    </row>
+    <row r="127" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D127" s="25"/>
+      <c r="E127" s="25"/>
+      <c r="F127" s="25"/>
+      <c r="G127" s="25"/>
+      <c r="H127" s="25"/>
+      <c r="I127" s="25"/>
+      <c r="J127" s="25"/>
+      <c r="K127" s="25"/>
+    </row>
+    <row r="128" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D128" s="25"/>
+      <c r="E128" s="25"/>
+      <c r="F128" s="25"/>
+      <c r="G128" s="25"/>
+      <c r="H128" s="25"/>
+      <c r="I128" s="25"/>
+      <c r="J128" s="25"/>
+      <c r="K128" s="25"/>
+    </row>
+    <row r="129" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D129" s="25"/>
+      <c r="E129" s="25"/>
+      <c r="F129" s="25"/>
+      <c r="G129" s="25"/>
+      <c r="H129" s="25"/>
+      <c r="I129" s="25"/>
+      <c r="J129" s="25"/>
+      <c r="K129" s="25"/>
+    </row>
+    <row r="130" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D130" s="25"/>
+      <c r="E130" s="25"/>
+      <c r="F130" s="25"/>
+      <c r="G130" s="25"/>
+      <c r="H130" s="25"/>
+      <c r="I130" s="25"/>
+      <c r="J130" s="25"/>
+      <c r="K130" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
